--- a/tests/master/Item-Group/ItemGroupImport.xlsx
+++ b/tests/master/Item-Group/ItemGroupImport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Thirumalvasan\Automacation Testing\playwrightMCP\tests\master\Item-Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24BE3C4-0CE3-4F48-944E-961774AD504F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98DC255-1F3A-45BA-87BA-6E30389EA8CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="3490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Item Group</t>
   </si>
@@ -28,31 +28,22 @@
     <t>Item Group Description</t>
   </si>
   <si>
-    <t>ITEM001</t>
-  </si>
-  <si>
-    <t>BUTTERSCOTCH</t>
-  </si>
-  <si>
-    <t>ITEM002</t>
-  </si>
-  <si>
-    <t>ITEM003</t>
-  </si>
-  <si>
-    <t>ITEM004</t>
-  </si>
-  <si>
-    <t>ITEM005</t>
-  </si>
-  <si>
-    <t>ITEM006</t>
-  </si>
-  <si>
-    <t>ITEM007</t>
-  </si>
-  <si>
-    <t>ITEM008</t>
+    <t>Cake Butter</t>
+  </si>
+  <si>
+    <t>Red Cake</t>
+  </si>
+  <si>
+    <t>White Cake</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>WC</t>
   </si>
 </sst>
 </file>
@@ -429,14 +420,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,74 +435,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
         <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>